--- a/学生信息导入模板.xlsx
+++ b/学生信息导入模板.xlsx
@@ -26,10 +26,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -41,12 +39,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="005B7FFF"/>
-        <bgColor rgb="005B7FFF"/>
+        <fgColor rgb="004A90D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -54,30 +51,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="00CCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="00CCCCCC"/>
-      </right>
-      <top style="thin">
-        <color rgb="00CCCCCC"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00CCCCCC"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -445,15 +425,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,69 +466,99 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>家长2</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>电话2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>住址</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>张三</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>2024001</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>男</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>张伟</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>13800138001</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>王芳</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>13700138002</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>重庆市渝中区xx路1号</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>李四</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>2024002</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>女</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>李强</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>13900139002</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>刘敏</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>13600139003</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>重庆市渝中区xx路2号</t>
         </is>

--- a/学生信息导入模板.xlsx
+++ b/学生信息导入模板.xlsx
@@ -456,22 +456,22 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>家长</t>
+          <t>父亲</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>电话</t>
+          <t>父亲电话</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>家长2</t>
+          <t>母亲</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>电话2</t>
+          <t>母亲电话</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
